--- a/src/main/resources/i18n/excel_user.xlsx
+++ b/src/main/resources/i18n/excel_user.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\User-Service\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1909DC-CF22-40AA-8FA5-2F8028CC4431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43B1F77-7870-48B0-8C27-15D605771E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="20835" windowHeight="9420" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>key</t>
   </si>
@@ -150,30 +150,6 @@
   </si>
   <si>
     <t>部門が見つかりません</t>
-  </si>
-  <si>
-    <t>TTCN</t>
-  </si>
-  <si>
-    <t>Information Technology Center</t>
-  </si>
-  <si>
-    <t>Trung tâm công nghệ</t>
-  </si>
-  <si>
-    <t>情報技術センター</t>
-  </si>
-  <si>
-    <t>TTR01</t>
-  </si>
-  <si>
-    <t>Bưu cục Thanh Trì</t>
-  </si>
-  <si>
-    <t>Thanh Tri Post Office</t>
-  </si>
-  <si>
-    <t>タンチ郵便局</t>
   </si>
   <si>
     <t>is_error</t>
@@ -584,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.25" bestFit="1" customWidth="1"/>
@@ -607,7 +583,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -765,36 +741,36 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
         <v>44</v>
       </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -811,40 +787,6 @@
         <v>50</v>
       </c>
       <c r="E13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" t="b">
         <v>1</v>
       </c>
     </row>
